--- a/bep.xlsx
+++ b/bep.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\수경\1. 요금\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\수경\github\vehicle_revenue_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="213">
   <si>
     <t>더 뉴 모닝</t>
   </si>
@@ -659,6 +659,12 @@
   <si>
     <t>bep(부가세제외)</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>더 뉴 캐스퍼</t>
+  </si>
+  <si>
+    <t>EV3 (EV) 스탠다드</t>
   </si>
 </sst>
 </file>
@@ -715,7 +721,18 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -991,10 +1008,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B210"/>
+  <dimension ref="A1:E212"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>209</v>
       </c>
@@ -1002,1680 +1019,1909 @@
         <v>210</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1">
         <v>1020000</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="1">
         <v>1060000</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1">
         <v>1000000</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1">
         <v>1010000</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="1">
         <v>1000000</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="1">
         <v>1010000</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="1">
         <v>1010000</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="1">
         <v>1000000</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="1">
         <v>1020000</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="1">
         <v>1000000</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="1">
         <v>1030000</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="1">
         <v>1030000</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="1">
         <v>1040000</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="1">
         <v>1030000</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="1">
         <v>1010000</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
       <c r="B17" s="1">
         <v>1010000</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
       <c r="B18" s="1">
         <v>1050000</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
       <c r="B19" s="1">
         <v>1050000</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
       <c r="B20" s="1">
         <v>1100000</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E20" s="1"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="1">
         <v>1060000</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>20</v>
       </c>
       <c r="B22" s="1">
         <v>1070000</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E22" s="1"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="1">
         <v>1070000</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E23" s="1"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
       </c>
       <c r="B24" s="1">
         <v>1110000</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E24" s="1"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>23</v>
       </c>
       <c r="B25" s="1">
         <v>1100000</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E25" s="1"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>24</v>
       </c>
       <c r="B26" s="1">
         <v>1060000</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E26" s="1"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
       <c r="B27" s="1">
         <v>1060000</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E27" s="1"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>26</v>
       </c>
       <c r="B28" s="1">
         <v>1110000</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E28" s="1"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>27</v>
       </c>
       <c r="B29" s="1">
         <v>1110000</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E29" s="1"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>28</v>
       </c>
       <c r="B30" s="1">
         <v>1060000</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E30" s="1"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="1">
         <v>1150000</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E31" s="1"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>30</v>
       </c>
       <c r="B32" s="1">
         <v>1120000</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E32" s="1"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>31</v>
       </c>
       <c r="B33" s="1">
         <v>1160000</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E33" s="1"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>32</v>
       </c>
       <c r="B34" s="1">
         <v>1190000</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E34" s="1"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>33</v>
       </c>
       <c r="B35" s="1">
         <v>1180000</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E35" s="1"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>34</v>
       </c>
       <c r="B36" s="1">
         <v>1210000</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>35</v>
       </c>
       <c r="B37" s="1">
         <v>1370000</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E37" s="1"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>36</v>
       </c>
       <c r="B38" s="1">
         <v>1280000</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E38" s="1"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>37</v>
       </c>
       <c r="B39" s="1">
         <v>1240000</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E39" s="1"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>38</v>
       </c>
       <c r="B40" s="1">
         <v>1170000</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E40" s="1"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>39</v>
       </c>
       <c r="B41" s="1">
         <v>1180000</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E41" s="1"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>40</v>
       </c>
       <c r="B42" s="1">
         <v>1070000</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E42" s="1"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>41</v>
       </c>
       <c r="B43" s="1">
         <v>1120000</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E43" s="1"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>42</v>
       </c>
       <c r="B44" s="1">
         <v>1180000</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E44" s="1"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>43</v>
       </c>
       <c r="B45" s="1">
         <v>1222000</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E45" s="1"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>44</v>
       </c>
       <c r="B46" s="1">
         <v>1220000</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E46" s="1"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>45</v>
       </c>
       <c r="B47" s="1">
         <v>1280000</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E47" s="1"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>46</v>
       </c>
       <c r="B48" s="1">
         <v>1110000</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E48" s="1"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>47</v>
       </c>
       <c r="B49" s="1">
         <v>1150000</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E49" s="1"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>48</v>
       </c>
       <c r="B50" s="1">
         <v>1150000</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E50" s="1"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>49</v>
       </c>
       <c r="B51" s="1">
         <v>1180000</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E51" s="1"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>50</v>
       </c>
       <c r="B52" s="1">
         <v>1200000</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E52" s="1"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>51</v>
       </c>
       <c r="B53" s="1">
         <v>1270000</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E53" s="1"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>52</v>
       </c>
       <c r="B54" s="1">
         <v>1100000</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E54" s="1"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>53</v>
       </c>
       <c r="B55" s="1">
         <v>1170000</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E55" s="1"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>54</v>
       </c>
       <c r="B56" s="1">
         <v>1170000</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E56" s="1"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>55</v>
       </c>
       <c r="B57" s="1">
         <v>1120000</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E57" s="1"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>56</v>
       </c>
       <c r="B58" s="1">
         <v>1120000</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E58" s="1"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>57</v>
       </c>
       <c r="B59" s="1">
         <v>1120000</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E59" s="1"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>58</v>
       </c>
       <c r="B60" s="1">
         <v>1170000</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E60" s="1"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>59</v>
       </c>
       <c r="B61" s="1">
         <v>1140000</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E61" s="1"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>60</v>
       </c>
       <c r="B62" s="1">
         <v>1250000</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E62" s="1"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>61</v>
       </c>
       <c r="B63" s="1">
         <v>1370000</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E63" s="1"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>62</v>
       </c>
       <c r="B64" s="1">
         <v>1270000</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E64" s="1"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>63</v>
       </c>
       <c r="B65" s="1">
         <v>1230000</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E65" s="1"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>64</v>
       </c>
       <c r="B66" s="1">
         <v>1240000</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E66" s="1"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>65</v>
       </c>
       <c r="B67" s="1">
         <v>1290000</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E67" s="1"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>66</v>
       </c>
       <c r="B68" s="1">
         <v>1340000</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E68" s="1"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>67</v>
       </c>
       <c r="B69" s="1">
         <v>1220000</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E69" s="1"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>68</v>
       </c>
       <c r="B70" s="1">
         <v>1210000</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E70" s="1"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>69</v>
       </c>
       <c r="B71" s="1">
         <v>1310000</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E71" s="1"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>70</v>
       </c>
       <c r="B72" s="1">
         <v>1200000</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E72" s="1"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>71</v>
       </c>
       <c r="B73" s="1">
         <v>1190000</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E73" s="1"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>72</v>
       </c>
       <c r="B74" s="1">
         <v>1230000</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E74" s="1"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>73</v>
       </c>
       <c r="B75" s="1">
         <v>1230000</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E75" s="1"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>74</v>
       </c>
       <c r="B76" s="1">
         <v>1240000</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E76" s="1"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>75</v>
       </c>
       <c r="B77" s="1">
         <v>1280000</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E77" s="1"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>76</v>
       </c>
       <c r="B78" s="1">
         <v>1260000</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E78" s="1"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>77</v>
       </c>
       <c r="B79" s="1">
         <v>1320000</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E79" s="1"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>78</v>
       </c>
       <c r="B80" s="1">
         <v>1350000</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E80" s="1"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>79</v>
       </c>
       <c r="B81" s="1">
         <v>1380000</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E81" s="1"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>80</v>
       </c>
       <c r="B82" s="1">
         <v>1260000</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E82" s="1"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>81</v>
       </c>
       <c r="B83" s="1">
         <v>1340000</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E83" s="1"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>82</v>
       </c>
       <c r="B84" s="1">
         <v>1400000</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E84" s="1"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>83</v>
       </c>
       <c r="B85" s="1">
         <v>1310000</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E85" s="1"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>84</v>
       </c>
       <c r="B86" s="1">
         <v>1240000</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E86" s="1"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>85</v>
       </c>
       <c r="B87" s="1">
         <v>1240000</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E87" s="1"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>86</v>
       </c>
       <c r="B88" s="1">
         <v>1280000</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E88" s="1"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>87</v>
       </c>
       <c r="B89" s="1">
         <v>1290000</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E89" s="1"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>88</v>
       </c>
       <c r="B90" s="1">
         <v>1410000</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E90" s="1"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>89</v>
       </c>
       <c r="B91" s="1">
         <v>1400000</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E91" s="1"/>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>90</v>
       </c>
       <c r="B92" s="1">
         <v>1430000</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E92" s="1"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>91</v>
       </c>
       <c r="B93" s="1">
         <v>1440000</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E93" s="1"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>92</v>
       </c>
       <c r="B94" s="1">
         <v>1300000</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E94" s="1"/>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>93</v>
       </c>
       <c r="B95" s="1">
         <v>1280000</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E95" s="1"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>94</v>
       </c>
       <c r="B96" s="1">
         <v>1300000</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E96" s="1"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>95</v>
       </c>
       <c r="B97" s="1">
         <v>1350000</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E97" s="1"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>96</v>
       </c>
       <c r="B98" s="1">
         <v>1360000</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E98" s="1"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>97</v>
       </c>
       <c r="B99" s="1">
         <v>1360000</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E99" s="1"/>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>98</v>
       </c>
       <c r="B100" s="1">
         <v>1440000</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E100" s="1"/>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>99</v>
       </c>
       <c r="B101" s="1">
         <v>1480000</v>
       </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E101" s="1"/>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>100</v>
       </c>
       <c r="B102" s="1">
         <v>1480000</v>
       </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E102" s="1"/>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>101</v>
       </c>
       <c r="B103" s="1">
         <v>1640000</v>
       </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E103" s="1"/>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>102</v>
       </c>
       <c r="B104" s="1">
         <v>1410000</v>
       </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E104" s="1"/>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>103</v>
       </c>
       <c r="B105" s="1">
         <v>1490000</v>
       </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E105" s="1"/>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>104</v>
       </c>
       <c r="B106" s="1">
         <v>1540000</v>
       </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E106" s="1"/>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>105</v>
       </c>
       <c r="B107" s="1">
         <v>1480000</v>
       </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E107" s="1"/>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>106</v>
       </c>
       <c r="B108" s="1">
         <v>1490000</v>
       </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E108" s="1"/>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>107</v>
       </c>
       <c r="B109" s="1">
         <v>1540000</v>
       </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E109" s="1"/>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>108</v>
       </c>
       <c r="B110" s="1">
         <v>1540000</v>
       </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E110" s="1"/>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>109</v>
       </c>
       <c r="B111" s="1">
         <v>1610000</v>
       </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E111" s="1"/>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>110</v>
       </c>
       <c r="B112" s="1">
         <v>1510000</v>
       </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E112" s="1"/>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>111</v>
       </c>
       <c r="B113" s="1">
         <v>1640000</v>
       </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E113" s="1"/>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>112</v>
       </c>
       <c r="B114" s="1">
         <v>1670000</v>
       </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E114" s="1"/>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>113</v>
       </c>
       <c r="B115" s="1">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E115" s="1"/>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>114</v>
       </c>
       <c r="B116" s="1">
         <v>2030000</v>
       </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E116" s="1"/>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>115</v>
       </c>
       <c r="B117" s="1">
         <v>1100000</v>
       </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E117" s="1"/>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>116</v>
       </c>
       <c r="B118" s="1">
         <v>1120000</v>
       </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E118" s="1"/>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>117</v>
       </c>
       <c r="B119" s="1">
         <v>1220000</v>
       </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E119" s="1"/>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>118</v>
       </c>
       <c r="B120" s="1">
         <v>1220000</v>
       </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E120" s="1"/>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>119</v>
       </c>
       <c r="B121" s="1">
         <v>1260000</v>
       </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E121" s="1"/>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>120</v>
       </c>
       <c r="B122" s="1">
         <v>1290000</v>
       </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E122" s="1"/>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>121</v>
       </c>
       <c r="B123" s="1">
         <v>1250000</v>
       </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E123" s="1"/>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>122</v>
       </c>
       <c r="B124" s="1">
         <v>1310000</v>
       </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E124" s="1"/>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>123</v>
       </c>
       <c r="B125" s="1">
         <v>1250000</v>
       </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E125" s="1"/>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>124</v>
       </c>
       <c r="B126" s="1">
         <v>1140000</v>
       </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E126" s="1"/>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>125</v>
       </c>
       <c r="B127" s="1">
         <v>1230000</v>
       </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E127" s="1"/>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>126</v>
       </c>
       <c r="B128" s="1">
         <v>1240000</v>
       </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E128" s="1"/>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>127</v>
       </c>
       <c r="B129" s="1">
         <v>1230000</v>
       </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E129" s="1"/>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>128</v>
       </c>
       <c r="B130" s="1">
         <v>1240000</v>
       </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E130" s="1"/>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>129</v>
       </c>
       <c r="B131" s="1">
         <v>1270000</v>
       </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E131" s="1"/>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>130</v>
       </c>
       <c r="B132" s="1">
         <v>1290000</v>
       </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E132" s="1"/>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>131</v>
       </c>
       <c r="B133" s="1">
         <v>1250000</v>
       </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E133" s="1"/>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>132</v>
       </c>
       <c r="B134" s="1">
         <v>1250000</v>
       </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E134" s="1"/>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>133</v>
       </c>
       <c r="B135" s="1">
         <v>1460000</v>
       </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E135" s="1"/>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>134</v>
       </c>
       <c r="B136" s="1">
         <v>1520000</v>
       </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E136" s="1"/>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>135</v>
       </c>
       <c r="B137" s="1">
         <v>1300000</v>
       </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E137" s="1"/>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>136</v>
       </c>
       <c r="B138" s="1">
         <v>1320000</v>
       </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E138" s="1"/>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>137</v>
       </c>
       <c r="B139" s="1">
         <v>1300000</v>
       </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E139" s="1"/>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>138</v>
       </c>
       <c r="B140" s="1">
         <v>1400000</v>
       </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E140" s="1"/>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>139</v>
       </c>
       <c r="B141" s="1">
         <v>1390000</v>
       </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E141" s="1"/>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>140</v>
       </c>
       <c r="B142" s="1">
         <v>1240000</v>
       </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E142" s="1"/>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>141</v>
       </c>
       <c r="B143" s="1">
         <v>1240000</v>
       </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E143" s="1"/>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>142</v>
       </c>
       <c r="B144" s="1">
         <v>1310000</v>
       </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E144" s="1"/>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>143</v>
       </c>
       <c r="B145" s="1">
         <v>1280000</v>
       </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E145" s="1"/>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>144</v>
       </c>
       <c r="B146" s="1">
         <v>1390000</v>
       </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E146" s="1"/>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>145</v>
       </c>
       <c r="B147" s="1">
         <v>1340000</v>
       </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E147" s="1"/>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>146</v>
       </c>
       <c r="B148" s="1">
         <v>1490000</v>
       </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E148" s="1"/>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>147</v>
       </c>
       <c r="B149" s="1">
         <v>1310000</v>
       </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E149" s="1"/>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>148</v>
       </c>
       <c r="B150" s="1">
         <v>1320000</v>
       </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E150" s="1"/>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>149</v>
       </c>
       <c r="B151" s="1">
         <v>1390000</v>
       </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E151" s="1"/>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>150</v>
       </c>
       <c r="B152" s="1">
         <v>1360000</v>
       </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E152" s="1"/>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>151</v>
       </c>
       <c r="B153" s="1">
         <v>1420000</v>
       </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E153" s="1"/>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>152</v>
       </c>
       <c r="B154" s="1">
         <v>1450000</v>
       </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E154" s="1"/>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>153</v>
       </c>
       <c r="B155" s="1">
         <v>1560000</v>
       </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E155" s="1"/>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>154</v>
       </c>
       <c r="B156" s="1">
         <v>1690000</v>
       </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E156" s="1"/>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>155</v>
       </c>
       <c r="B157" s="1">
         <v>1440000</v>
       </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E157" s="1"/>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>156</v>
       </c>
       <c r="B158" s="1">
         <v>1560000</v>
       </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E158" s="1"/>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>157</v>
       </c>
       <c r="B159" s="1">
         <v>1600000</v>
       </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E159" s="1"/>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>158</v>
       </c>
       <c r="B160" s="1">
         <v>2110000</v>
       </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E160" s="1"/>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>159</v>
       </c>
       <c r="B161" s="1">
         <v>2350000</v>
       </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E161" s="1"/>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>160</v>
       </c>
       <c r="B162" s="1">
         <v>1750000</v>
       </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E162" s="1"/>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>161</v>
       </c>
       <c r="B163" s="1">
         <v>1210000</v>
       </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E163" s="1"/>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>162</v>
       </c>
       <c r="B164" s="1">
         <v>1380000</v>
       </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E164" s="1"/>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>163</v>
       </c>
       <c r="B165" s="1">
         <v>1400000</v>
       </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E165" s="1"/>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>164</v>
       </c>
       <c r="B166" s="1">
         <v>1410000</v>
       </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E166" s="1"/>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>165</v>
       </c>
       <c r="B167" s="1">
         <v>1520000</v>
       </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E167" s="1"/>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>166</v>
       </c>
       <c r="B168" s="1">
         <v>1470000</v>
       </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E168" s="1"/>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>167</v>
       </c>
       <c r="B169" s="1">
         <v>1430000</v>
       </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E169" s="1"/>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>168</v>
       </c>
       <c r="B170" s="1">
         <v>1490000</v>
       </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E170" s="1"/>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>169</v>
       </c>
       <c r="B171" s="1">
         <v>1820000</v>
       </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E171" s="1"/>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>170</v>
       </c>
       <c r="B172" s="1">
         <v>1820000</v>
       </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E172" s="1"/>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>171</v>
       </c>
       <c r="B173" s="1">
         <v>2250000</v>
       </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E173" s="1"/>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>172</v>
       </c>
       <c r="B174" s="1">
         <v>1320000</v>
       </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E174" s="1"/>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>173</v>
       </c>
       <c r="B175" s="1">
         <v>1770000</v>
       </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E175" s="1"/>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>174</v>
       </c>
       <c r="B176" s="1">
         <v>1340000</v>
       </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E176" s="1"/>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>175</v>
       </c>
       <c r="B177" s="1">
         <v>1340000</v>
       </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E177" s="1"/>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>176</v>
       </c>
       <c r="B178" s="1">
         <v>1340000</v>
       </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E178" s="1"/>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>177</v>
       </c>
       <c r="B179" s="1">
         <v>1410000</v>
       </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E179" s="1"/>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>178</v>
       </c>
       <c r="B180" s="1">
         <v>1140000</v>
       </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E180" s="1"/>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>179</v>
       </c>
       <c r="B181" s="1">
         <v>1480000</v>
       </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E181" s="1"/>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>180</v>
       </c>
       <c r="B182" s="1">
         <v>2000000</v>
       </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E182" s="1"/>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>181</v>
       </c>
       <c r="B183" s="1">
         <v>1340000</v>
       </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E183" s="1"/>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>182</v>
       </c>
       <c r="B184" s="1">
         <v>1340000</v>
       </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E184" s="1"/>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>183</v>
       </c>
       <c r="B185" s="1">
         <v>1590000</v>
       </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E185" s="1"/>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>184</v>
       </c>
       <c r="B186" s="1">
         <v>1560000</v>
       </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E186" s="1"/>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>185</v>
       </c>
       <c r="B187" s="1">
         <v>1830000</v>
       </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E187" s="1"/>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>186</v>
       </c>
       <c r="B188" s="1">
         <v>1620000</v>
       </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E188" s="1"/>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>187</v>
       </c>
       <c r="B189" s="1">
         <v>1620000</v>
       </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E189" s="1"/>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>188</v>
       </c>
       <c r="B190" s="1">
         <v>1590000</v>
       </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E190" s="1"/>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>189</v>
       </c>
       <c r="B191" s="1">
         <v>2390000</v>
       </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E191" s="1"/>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>190</v>
       </c>
       <c r="B192" s="1">
         <v>1050000</v>
       </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E192" s="1"/>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>191</v>
       </c>
       <c r="B193" s="1">
         <v>1070000</v>
       </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E193" s="1"/>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>192</v>
       </c>
       <c r="B194" s="1">
         <v>1120000</v>
       </c>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E194" s="1"/>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>193</v>
       </c>
       <c r="B195" s="1">
         <v>1260000</v>
       </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E195" s="1"/>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>194</v>
       </c>
       <c r="B196" s="1">
         <v>1270000</v>
       </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E196" s="1"/>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>195</v>
       </c>
       <c r="B197" s="1">
         <v>1330000</v>
       </c>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E197" s="1"/>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>196</v>
       </c>
       <c r="B198" s="1">
         <v>1580000</v>
       </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E198" s="1"/>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>197</v>
       </c>
       <c r="B199" s="1">
         <v>1590000</v>
       </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E199" s="1"/>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>198</v>
       </c>
       <c r="B200" s="1">
         <v>1670000</v>
       </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E200" s="1"/>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>199</v>
       </c>
       <c r="B201" s="1">
         <v>1570000</v>
       </c>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E201" s="1"/>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>200</v>
       </c>
       <c r="B202" s="1">
         <v>1580000</v>
       </c>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E202" s="1"/>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>201</v>
       </c>
       <c r="B203" s="1">
         <v>1580000</v>
       </c>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E203" s="1"/>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>202</v>
       </c>
       <c r="B204" s="1">
         <v>1710000</v>
       </c>
-    </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E204" s="1"/>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>203</v>
       </c>
       <c r="B205" s="1">
         <v>1470000</v>
       </c>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E205" s="1"/>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>204</v>
       </c>
       <c r="B206" s="1">
         <v>1540000</v>
       </c>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E206" s="1"/>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>205</v>
       </c>
       <c r="B207" s="1">
         <v>1630000</v>
       </c>
-    </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E207" s="1"/>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>206</v>
       </c>
       <c r="B208" s="1">
         <v>1720000</v>
       </c>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E208" s="1"/>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>207</v>
       </c>
       <c r="B209" s="1">
         <v>1800000</v>
       </c>
-    </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E209" s="1"/>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>208</v>
       </c>
       <c r="B210" s="1">
         <v>2180000</v>
       </c>
+      <c r="E210" s="1"/>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>211</v>
+      </c>
+      <c r="B211" s="1">
+        <v>1090000</v>
+      </c>
+      <c r="E211" s="1"/>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>212</v>
+      </c>
+      <c r="B212" s="1">
+        <v>1470000</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>